--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-09).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-09).xlsx
@@ -935,10 +935,10 @@
     <t>214</t>
   </si>
   <si>
-    <t>24</t>
+    <t>19</t>
   </si>
   <si>
-    <t>R$ 3.629,94</t>
+    <t>R$ 3.628,48</t>
   </si>
   <si>
     <t>41.0</t>
@@ -947,7 +947,7 @@
     <t>25.8</t>
   </si>
   <si>
-    <t>4.75</t>
+    <t>4.74</t>
   </si>
   <si>
     <t>18.6</t>
@@ -959,10 +959,10 @@
     <t>6.3</t>
   </si>
   <si>
-    <t>45.4%</t>
+    <t>46.3%</t>
   </si>
   <si>
-    <t>19.1%</t>
+    <t>19.0%</t>
   </si>
   <si>
     <t>2.2%</t>
@@ -980,7 +980,7 @@
     <t>0.1%</t>
   </si>
   <si>
-    <t>6.9%</t>
+    <t>6.8%</t>
   </si>
   <si>
     <t>2.5%</t>
@@ -989,13 +989,13 @@
     <t>3.6%</t>
   </si>
   <si>
-    <t>1129.0</t>
+    <t>1131.0</t>
   </si>
   <si>
-    <t>920.0</t>
+    <t>922.0</t>
   </si>
   <si>
-    <t>107.0</t>
+    <t>108.0</t>
   </si>
   <si>
     <t>19.0</t>
@@ -1010,7 +1010,7 @@
     <t>330.0</t>
   </si>
   <si>
-    <t>122.0</t>
+    <t>123.0</t>
   </si>
   <si>
     <t>173.0</t>
@@ -2206,7 +2206,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>51</v>
@@ -2236,14 +2236,26 @@
         <v>58</v>
       </c>
       <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
+      <c r="M6" s="5">
+        <v>6765.5600000000004</v>
+      </c>
+      <c r="N6" s="6">
+        <v>79</v>
+      </c>
       <c r="O6" s="6"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
+      <c r="P6" s="7">
+        <v>4.8557013157894735</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>14.471857377049181</v>
+      </c>
+      <c r="R6" s="8">
+        <v>2.5412573770491802</v>
+      </c>
       <c r="S6" s="8"/>
-      <c r="T6" s="9"/>
+      <c r="T6" s="9">
+        <v>0.65573770491803274</v>
+      </c>
       <c r="U6" s="9"/>
       <c r="V6" s="9"/>
       <c r="W6" s="9"/>
@@ -4958,7 +4970,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>51</v>
@@ -4988,14 +5000,26 @@
         <v>58</v>
       </c>
       <c r="L24" s="4"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="6"/>
+      <c r="M24" s="5">
+        <v>3507.98</v>
+      </c>
+      <c r="N24" s="6">
+        <v>42</v>
+      </c>
       <c r="O24" s="6"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
+      <c r="P24" s="7">
+        <v>3.1264219512195122</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>20.127142857142857</v>
+      </c>
+      <c r="R24" s="8">
+        <v>10.023808571428571</v>
+      </c>
       <c r="S24" s="8"/>
-      <c r="T24" s="9"/>
+      <c r="T24" s="9">
+        <v>0.31428571428571428</v>
+      </c>
       <c r="U24" s="9"/>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -6782,7 +6806,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6812,14 +6836,26 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
+      <c r="M36" s="5">
+        <v>2942.02</v>
+      </c>
+      <c r="N36" s="6">
+        <v>34</v>
+      </c>
       <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
+      <c r="P36" s="7">
+        <v>4.9515624999999996</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>18.267542105263157</v>
+      </c>
+      <c r="R36" s="8">
+        <v>7</v>
+      </c>
       <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
+      <c r="T36" s="9">
+        <v>0.36842105263157893</v>
+      </c>
       <c r="U36" s="9"/>
       <c r="V36" s="9"/>
       <c r="W36" s="9"/>
@@ -9071,7 +9107,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9101,14 +9137,26 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>158.30000000000001</v>
+      </c>
+      <c r="N51" s="6">
+        <v>2</v>
+      </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
+      <c r="P51" s="7">
+        <v>4.2000000000000002</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>18.858350000000002</v>
+      </c>
+      <c r="R51" s="8">
+        <v>7.7333499999999997</v>
+      </c>
       <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
+      <c r="T51" s="9">
+        <v>0</v>
+      </c>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
@@ -14773,7 +14821,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14801,14 +14849,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>4491.25</v>
+      </c>
+      <c r="N89" s="6">
+        <v>41</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>4.9987804878048774</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>19.690000000000001</v>
+      </c>
+      <c r="R89" s="8">
+        <v>6.4091649999999998</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.25</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
@@ -18015,7 +18075,9 @@
       <c r="N111" s="6">
         <v>16</v>
       </c>
-      <c r="O111" s="6"/>
+      <c r="O111" s="6">
+        <v>16</v>
+      </c>
       <c r="P111" s="7">
         <v>4.3041687499999997</v>
       </c>
@@ -18025,31 +18087,75 @@
       <c r="R111" s="8">
         <v>3.9197937500000002</v>
       </c>
-      <c r="S111" s="8"/>
+      <c r="S111" s="8">
+        <v>7</v>
+      </c>
       <c r="T111" s="9">
         <v>0.5625</v>
       </c>
-      <c r="U111" s="9"/>
-      <c r="V111" s="9"/>
-      <c r="W111" s="9"/>
-      <c r="X111" s="9"/>
-      <c r="Y111" s="9"/>
-      <c r="Z111" s="9"/>
-      <c r="AA111" s="9"/>
-      <c r="AB111" s="9"/>
-      <c r="AC111" s="9"/>
-      <c r="AD111" s="6"/>
-      <c r="AE111" s="6"/>
-      <c r="AF111" s="6"/>
-      <c r="AG111" s="6"/>
-      <c r="AH111" s="6"/>
-      <c r="AI111" s="6"/>
-      <c r="AJ111" s="6"/>
-      <c r="AK111" s="6"/>
-      <c r="AL111" s="6"/>
-      <c r="AM111" s="6"/>
-      <c r="AN111" s="9"/>
-      <c r="AO111" s="6"/>
+      <c r="U111" s="9">
+        <v>0</v>
+      </c>
+      <c r="V111" s="9">
+        <v>0</v>
+      </c>
+      <c r="W111" s="9">
+        <v>0</v>
+      </c>
+      <c r="X111" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y111" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO111" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP111" s="4">
         <v>58</v>
       </c>
@@ -28337,7 +28443,9 @@
       <c r="N179" s="6">
         <v>39</v>
       </c>
-      <c r="O179" s="6"/>
+      <c r="O179" s="6">
+        <v>22</v>
+      </c>
       <c r="P179" s="7">
         <v>2.4470076923076922</v>
       </c>
@@ -28347,31 +28455,75 @@
       <c r="R179" s="8">
         <v>1.6651499999999999</v>
       </c>
-      <c r="S179" s="8"/>
+      <c r="S179" s="8">
+        <v>7</v>
+      </c>
       <c r="T179" s="9">
         <v>1</v>
       </c>
-      <c r="U179" s="9"/>
-      <c r="V179" s="9"/>
-      <c r="W179" s="9"/>
-      <c r="X179" s="9"/>
-      <c r="Y179" s="9"/>
-      <c r="Z179" s="9"/>
-      <c r="AA179" s="9"/>
-      <c r="AB179" s="9"/>
-      <c r="AC179" s="9"/>
-      <c r="AD179" s="6"/>
-      <c r="AE179" s="6"/>
-      <c r="AF179" s="6"/>
-      <c r="AG179" s="6"/>
-      <c r="AH179" s="6"/>
-      <c r="AI179" s="6"/>
-      <c r="AJ179" s="6"/>
-      <c r="AK179" s="6"/>
-      <c r="AL179" s="6"/>
-      <c r="AM179" s="6"/>
-      <c r="AN179" s="9"/>
-      <c r="AO179" s="6"/>
+      <c r="U179" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="V179" s="9">
+        <v>0.045454545454545456</v>
+      </c>
+      <c r="W179" s="9">
+        <v>0</v>
+      </c>
+      <c r="X179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB179" s="9">
+        <v>0.045454545454545456</v>
+      </c>
+      <c r="AC179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD179" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE179" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO179" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP179" s="4">
         <v>58</v>
       </c>
